--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486904_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486904_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.754899999999999</v>
+        <v>7.5408</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7242</v>
+        <v>7.3915</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0307</v>
+        <v>0.1492</v>
       </c>
       <c r="G2" t="n">
         <v>3.6777</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>3.221</v>
+        <v>2.0069</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1224</v>
+        <v>1.7897</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2171</v>
       </c>
       <c r="V2" t="n">
         <v>0.8295</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5027</v>
+        <v>4.9548</v>
       </c>
       <c r="E3" t="n">
-        <v>5.433</v>
+        <v>5.9444</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9303</v>
+        <v>-0.9896</v>
       </c>
       <c r="G3" t="n">
         <v>2.5547</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9213</v>
+        <v>1.3735</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6274</v>
+        <v>1.1388</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2939</v>
+        <v>0.2346</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. NDOUR</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9751</v>
+        <v>3.6611</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1217</v>
+        <v>3.9099</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1466</v>
+        <v>-0.2488</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6513</v>
+        <v>0.6218</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7613</v>
+        <v>4.0292</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.11</v>
+        <v>-3.4075</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2661</v>
+        <v>2.4021</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1477</v>
+        <v>5.139</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1184</v>
+        <v>-2.7369</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6147</v>
+        <v>-1.7803</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3863</v>
+        <v>-1.1098</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2284</v>
+        <v>-0.6706</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5641</v>
+        <v>1.4151</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7859</v>
+        <v>1.321</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7782</v>
+        <v>0.0941</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8295</v>
+        <v>1.4189</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6982</v>
+        <v>1.4189</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>O. NDOUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8268</v>
+        <v>2.4374</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0459</v>
+        <v>2.9396</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2191</v>
+        <v>-0.5023</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6218</v>
+        <v>1.6513</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0292</v>
+        <v>2.7613</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.4075</v>
+        <v>-1.11</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4021</v>
+        <v>3.2661</v>
       </c>
       <c r="K5" t="n">
-        <v>5.139</v>
+        <v>3.1477</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.7369</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7803</v>
+        <v>-1.6147</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1098</v>
+        <v>-0.3863</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6706</v>
+        <v>-1.2284</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5808</v>
+        <v>2.0263</v>
       </c>
       <c r="T5" t="n">
-        <v>0.457</v>
+        <v>1.6038</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1238</v>
+        <v>0.4225</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4189</v>
+        <v>-0.8295</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4189</v>
+        <v>-0.6982</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1314</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1582</v>
+        <v>0.3296</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1893</v>
+        <v>-0.5732</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3475</v>
+        <v>0.9028</v>
       </c>
       <c r="G6" t="n">
         <v>-0.642</v>
@@ -922,13 +922,13 @@
         <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4318</v>
+        <v>-0.2604</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8486</v>
+        <v>-0.2326</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4168</v>
+        <v>-0.0279</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. LLORACH CORNELLES</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1013</v>
+        <v>0.2665</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1317</v>
+        <v>1.3749</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0304</v>
+        <v>-1.1084</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0552</v>
+        <v>0.5084</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0552</v>
+        <v>0.6586</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.1502</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.5416</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.4366</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.895</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0552</v>
+        <v>-1.0332</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0552</v>
+        <v>-1.778</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.7449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2515</v>
+        <v>-0.741</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1317</v>
+        <v>-0.4069</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1197</v>
+        <v>-0.334</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9384</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1181</v>
+        <v>0.1738</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1386</v>
+        <v>-1.5824</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2566</v>
+        <v>1.7562</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5084</v>
+        <v>-0.3754</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6586</v>
+        <v>-1.5701</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1502</v>
+        <v>1.1947</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5416</v>
+        <v>-1.16</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4366</v>
+        <v>-0.5416</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.895</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0332</v>
+        <v>0.7846</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.778</v>
+        <v>-1.0285</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7449</v>
+        <v>1.8131</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1255</v>
+        <v>-0.4775</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6433</v>
+        <v>-0.217</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4823</v>
+        <v>-0.2604</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9384</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>P. LLORACH CORNELLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3293</v>
+        <v>-0.0058</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8188</v>
+        <v>-0.0659</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4895</v>
+        <v>0.0601</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3754</v>
+        <v>-0.0552</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5701</v>
+        <v>-0.0552</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1947</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5416</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7846</v>
+        <v>-0.0552</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0285</v>
+        <v>-0.0552</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8131</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9806</v>
+        <v>-0.1559</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4534</v>
+        <v>-0.0659</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5272</v>
+        <v>-0.0901</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0184</v>
+        <v>-0.3736</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0897</v>
+        <v>0.2602</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1081</v>
+        <v>-0.6338</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6866</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4361</v>
+        <v>1.0809</v>
       </c>
       <c r="T10" t="n">
-        <v>0.825</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3889</v>
+        <v>0.0854</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1072</v>
+        <v>-1.2192</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5463</v>
+        <v>0.6122</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6535</v>
+        <v>-1.8314</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5586</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2735</v>
+        <v>-0.3855</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3952</v>
+        <v>-0.3294</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1217</v>
+        <v>-0.0561</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4805</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4194</v>
+        <v>-1.3239</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0659</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3535</v>
+        <v>-1.3239</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0552</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1856</v>
+        <v>-0.0901</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0659</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1786</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.124</v>
+        <v>16.4415</v>
       </c>
       <c r="E13" t="n">
-        <v>18.8937</v>
+        <v>20.2112</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7696</v>
+        <v>-3.7699</v>
       </c>
       <c r="G13" t="n">
         <v>4.640899999999999</v>
@@ -1468,13 +1468,13 @@
         <v>11.2939</v>
       </c>
       <c r="S13" t="n">
-        <v>4.474799999999999</v>
+        <v>5.792299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.279599999999999</v>
+        <v>5.597</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1952</v>
+        <v>0.1950999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1786</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.436</v>
+        <v>3.2669</v>
       </c>
       <c r="E14" t="n">
-        <v>3.651</v>
+        <v>3.2326</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.215</v>
+        <v>0.0343</v>
       </c>
       <c r="G14" t="n">
         <v>2.7192</v>
@@ -1546,13 +1546,13 @@
         <v>0.616</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5381</v>
+        <v>0.369</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6701</v>
+        <v>0.2517</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.132</v>
+        <v>0.1173</v>
       </c>
       <c r="V14" t="n">
         <v>0.5893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8411</v>
+        <v>2.9474</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5136</v>
+        <v>3.409</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6725</v>
+        <v>-0.4615</v>
       </c>
       <c r="G15" t="n">
         <v>2.6578</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4327</v>
+        <v>-0.3264</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0931</v>
+        <v>-0.1977</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3396</v>
+        <v>-0.1287</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0909</v>
+        <v>1.2152</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9567</v>
+        <v>2.8168</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8658</v>
+        <v>-1.6016</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0417</v>
+        <v>2.0486</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0176</v>
+        <v>-2.177</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9759</v>
+        <v>4.2255</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5977</v>
+        <v>4.1179</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3214</v>
+        <v>-0.0126</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2763</v>
+        <v>4.1305</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.556</v>
+        <v>-2.0693</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.3038</v>
+        <v>-2.1643</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2522</v>
+        <v>0.095</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.616</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8829</v>
+        <v>-0.7923</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3016</v>
+        <v>-0.4263</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4187</v>
+        <v>-0.366</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2177</v>
+        <v>1.3963</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9159</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6982</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2494</v>
+        <v>0.5034</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1891</v>
+        <v>3.1199</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9398</v>
+        <v>-2.6165</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0486</v>
+        <v>1.0417</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.177</v>
+        <v>2.0176</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2255</v>
+        <v>-0.9759</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1179</v>
+        <v>4.5977</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0126</v>
+        <v>4.3214</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1305</v>
+        <v>0.2763</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0693</v>
+        <v>-3.556</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.1643</v>
+        <v>-2.3038</v>
       </c>
       <c r="O17" t="n">
-        <v>0.095</v>
+        <v>-1.2522</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4374</v>
+        <v>-0.616</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7581</v>
+        <v>0.2954</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.054</v>
+        <v>0.4648</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7042</v>
+        <v>-0.1694</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3963</v>
+        <v>-0.2177</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>-0.9159</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2177</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5216</v>
+        <v>-0.8197</v>
       </c>
       <c r="E18" t="n">
-        <v>0.676</v>
+        <v>0.4668</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1976</v>
+        <v>-1.2865</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0047</v>
@@ -1858,13 +1858,13 @@
         <v>0.2053</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2778</v>
+        <v>-0.0203</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5656</v>
+        <v>0.3564</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2878</v>
+        <v>-0.3767</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0113</v>
+        <v>-2.5313</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4746</v>
+        <v>-1.1656</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5367</v>
+        <v>-1.3657</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4883</v>
+        <v>-0.3811</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1621</v>
+        <v>-0.3861</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3261</v>
+        <v>0.005</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1449</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1714</v>
+        <v>0.9183</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0264</v>
+        <v>-0.8556</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6332</v>
+        <v>-0.4438</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3335</v>
+        <v>-1.3044</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2997</v>
+        <v>0.8606</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8481</v>
+        <v>-0.616</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3251</v>
+        <v>-0.3555</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4339</v>
+        <v>-0.2016</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1088</v>
+        <v>-0.1539</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1432</v>
+        <v>-2.7331</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6886</v>
+        <v>-1.4946</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4546</v>
+        <v>-1.2385</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3811</v>
+        <v>-3.2833</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3861</v>
+        <v>-2.7124</v>
       </c>
       <c r="I20" t="n">
-        <v>0.005</v>
+        <v>-0.5709</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06270000000000001</v>
+        <v>-1.2929</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9183</v>
+        <v>-1.1611</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8556</v>
+        <v>-0.1318</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4438</v>
+        <v>-1.9904</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3044</v>
+        <v>-1.5513</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8606</v>
+        <v>-0.4391</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9674</v>
+        <v>0.1395</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7246</v>
+        <v>-0.2017</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2428</v>
+        <v>0.3411</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1799</v>
+        <v>-3.0716</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3212</v>
+        <v>-1.6943</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8587</v>
+        <v>-1.3773</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2562</v>
+        <v>-2.8273</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1033</v>
+        <v>-2.4722</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1529</v>
+        <v>-0.3552</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2207</v>
+        <v>-1.5129</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7008</v>
+        <v>-0.947</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9215</v>
+        <v>-0.5659</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0355</v>
+        <v>-1.3144</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8041</v>
+        <v>-1.5252</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.2107</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4374</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1372</v>
+        <v>-0.3961</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4725</v>
+        <v>-0.3333</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6097</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2142</v>
+        <v>-3.1107</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.913</v>
+        <v>-0.6838</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3012</v>
+        <v>-2.4268</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2833</v>
+        <v>-1.4883</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7124</v>
+        <v>-0.1621</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5709</v>
+        <v>-1.3261</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2929</v>
+        <v>1.1449</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1611</v>
+        <v>1.1714</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1318</v>
+        <v>-0.0264</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9904</v>
+        <v>-2.6332</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5513</v>
+        <v>-1.3335</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4391</v>
+        <v>-1.2997</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4107</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3416</v>
+        <v>0.2257</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6201</v>
+        <v>0.2247</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2784</v>
+        <v>0.001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1612</v>
+        <v>-3.1764</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2173</v>
+        <v>-1.635</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9439</v>
+        <v>-1.5414</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8273</v>
+        <v>-1.2562</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4722</v>
+        <v>-1.1033</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3552</v>
+        <v>-0.1529</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5129</v>
+        <v>-0.2207</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.947</v>
+        <v>0.7008</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5659</v>
+        <v>-0.9215</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3144</v>
+        <v>-1.0355</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5252</v>
+        <v>-1.8041</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2107</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0267</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4858</v>
+        <v>-0.1337</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8563</v>
+        <v>0.1587</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6294</v>
+        <v>-0.2924</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.51</v>
+        <v>-4.8248</v>
       </c>
       <c r="E24" t="n">
         <v>-2.6019</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.908</v>
+        <v>-2.2228</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8672</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3758</v>
+        <v>-0.6906</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2907</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0851</v>
+        <v>-0.3999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2402</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.124</v>
+        <v>-12.3347</v>
       </c>
       <c r="E25" t="n">
-        <v>3.769799999999999</v>
+        <v>3.7699</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.8938</v>
+        <v>-16.1043</v>
       </c>
       <c r="G25" t="n">
         <v>-4.6408</v>
@@ -2404,13 +2404,13 @@
         <v>4.1067</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.4747</v>
+        <v>-1.6853</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1950999999999999</v>
+        <v>-0.195</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.2797</v>
+        <v>-1.4904</v>
       </c>
       <c r="V25" t="n">
         <v>1.1786</v>
@@ -2419,7 +2419,7 @@
         <v>3.6897</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.511000000000001</v>
+        <v>-2.511</v>
       </c>
     </row>
   </sheetData>
